--- a/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
+++ b/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2148486011203608</v>
+        <v>-0.2148486011203609</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5398665182943801</v>
+        <v>0.53986651829438</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.213735291042608</v>
+        <v>0.2137352910426079</v>
       </c>
     </row>
     <row r="14">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.325687326512341</v>
+        <v>-0.3256873265123409</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.800579385935314</v>
+        <v>-0.8005793859353137</v>
       </c>
     </row>
     <row r="3">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3785271549791805</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.04772330740818</v>
+        <v>-1.047723307408179</v>
       </c>
     </row>
     <row r="6">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.2148486011203608</v>
+        <v>-0.2148486011203609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.282161403908384</v>
+        <v>-0.2821614039083842</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06489355131175112</v>
+        <v>-0.06489355131175117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4192125431629353</v>
+        <v>0.419212543162935</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04127688761109256</v>
+        <v>0.04127688761109307</v>
       </c>
     </row>
     <row r="10">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.05235333367165</v>
+        <v>-1.052353333671649</v>
       </c>
     </row>
     <row r="13">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8718797997519854</v>
+        <v>-0.8718797997519848</v>
       </c>
     </row>
     <row r="14">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.146189229938508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03897412457640573</v>
+        <v>0.03897412457640598</v>
       </c>
     </row>
     <row r="16">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1957735252430408</v>
+        <v>-0.1957735252430409</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1929429262656746</v>
+        <v>-0.1929429262656749</v>
       </c>
     </row>
     <row r="17">
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6325945707458291</v>
+        <v>-0.6325945707458294</v>
       </c>
     </row>
     <row r="18">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1768006485748422</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.549671405169005</v>
+        <v>1.549671405169004</v>
       </c>
     </row>
     <row r="20">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.130172268944158</v>
+        <v>0.1301722689441583</v>
       </c>
     </row>
     <row r="21">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6256843559636339</v>
+        <v>0.6256843559636334</v>
       </c>
     </row>
     <row r="22">

--- a/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
+++ b/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.53986651829438</v>
+        <v>0.5398665182943803</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2137352910426079</v>
+        <v>0.213735291042608</v>
       </c>
     </row>
     <row r="14">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.192262238325701</v>
+        <v>0.1922622383257012</v>
       </c>
     </row>
   </sheetData>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3256873265123409</v>
+        <v>-0.325687326512341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8005793859353137</v>
+        <v>-0.8005793859353139</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02456567791523656</v>
+        <v>-0.02456567791523645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6078351989334906</v>
+        <v>0.6078351989334912</v>
       </c>
     </row>
     <row r="4">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2821614039083842</v>
+        <v>-0.2821614039083844</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.419212543162935</v>
+        <v>0.4192125431629352</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04127688761109307</v>
+        <v>0.04127688761109268</v>
       </c>
     </row>
     <row r="10">
@@ -1046,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.207626454050305</v>
+        <v>-0.2076264540503049</v>
       </c>
     </row>
     <row r="11">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927821</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8718797997519848</v>
+        <v>-0.8718797997519847</v>
       </c>
     </row>
     <row r="14">
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03897412457640598</v>
+        <v>0.03897412457640612</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1929429262656749</v>
+        <v>-0.1929429262656748</v>
       </c>
     </row>
     <row r="17">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821826</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6325945707458294</v>
+        <v>-0.6325945707458287</v>
       </c>
     </row>
     <row r="18">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1301722689441583</v>
+        <v>0.1301722689441582</v>
       </c>
     </row>
     <row r="21">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060786</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6256843559636334</v>
+        <v>0.625684355963634</v>
       </c>
     </row>
     <row r="22">

--- a/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
+++ b/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1922622383257012</v>
+        <v>0.192262238325701</v>
       </c>
     </row>
   </sheetData>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8005793859353139</v>
+        <v>-0.8005793859353137</v>
       </c>
     </row>
     <row r="3">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6078351989334912</v>
+        <v>0.6078351989334914</v>
       </c>
     </row>
     <row r="4">
@@ -770,7 +770,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.217897943449718</v>
+        <v>1.217897943449719</v>
       </c>
     </row>
     <row r="5">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3785271549791803</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2821614039083844</v>
+        <v>-0.2821614039083842</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06489355131175117</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4192125431629352</v>
+        <v>0.4192125431629363</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04127688761109268</v>
+        <v>0.04127688761109281</v>
       </c>
     </row>
     <row r="10">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2076264540503049</v>
+        <v>-0.2076264540503053</v>
       </c>
     </row>
     <row r="11">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1915672065927821</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.052353333671649</v>
+        <v>-1.052353333671648</v>
       </c>
     </row>
     <row r="13">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3409314871343582</v>
+        <v>-0.3409314871343583</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8718797997519847</v>
+        <v>-0.8718797997519852</v>
       </c>
     </row>
     <row r="14">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.146189229938508</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03897412457640612</v>
+        <v>0.03897412457640573</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1929429262656748</v>
+        <v>-0.1929429262656746</v>
       </c>
     </row>
     <row r="17">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2897718616821826</v>
+        <v>-0.2897718616821827</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6325945707458287</v>
+        <v>-0.6325945707458291</v>
       </c>
     </row>
     <row r="18">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1537779986546591</v>
+        <v>0.153777998654659</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1301722689441582</v>
+        <v>0.1301722689441586</v>
       </c>
     </row>
     <row r="21">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.625684355963634</v>
+        <v>0.6256843559636336</v>
       </c>
     </row>
     <row r="22">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
+++ b/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5398665182943803</v>
+        <v>0.53986651829438</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.213735291042608</v>
+        <v>0.2137352910426079</v>
       </c>
     </row>
     <row r="14">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.192262238325701</v>
+        <v>0.1922622383257009</v>
       </c>
     </row>
   </sheetData>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8005793859353137</v>
+        <v>-0.800579385935314</v>
       </c>
     </row>
     <row r="3">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1058668675511346</v>
+        <v>0.1058668675511344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.217897943449719</v>
+        <v>1.217897943449718</v>
       </c>
     </row>
     <row r="5">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4000280024741704</v>
+        <v>-0.4000280024741703</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06489355131175095</v>
+        <v>-0.06489355131175106</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4192125431629363</v>
+        <v>0.4192125431629357</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04127688761109281</v>
+        <v>0.04127688761109321</v>
       </c>
     </row>
     <row r="10">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1989128906978095</v>
+        <v>-0.1989128906978094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2076264540503053</v>
+        <v>-0.2076264540503049</v>
       </c>
     </row>
     <row r="11">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927819</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755897</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.052353333671648</v>
+        <v>-1.052353333671649</v>
       </c>
     </row>
     <row r="13">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8718797997519852</v>
+        <v>-0.8718797997519848</v>
       </c>
     </row>
     <row r="14">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.1461892299385082</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03897412457640573</v>
+        <v>0.03897412457640534</v>
       </c>
     </row>
     <row r="16">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1957735252430409</v>
+        <v>-0.195773525243041</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1929429262656746</v>
+        <v>-0.1929429262656753</v>
       </c>
     </row>
     <row r="17">
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6325945707458291</v>
+        <v>-0.6325945707458293</v>
       </c>
     </row>
     <row r="18">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.176800648574842</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1301722689441586</v>
+        <v>0.1301722689441585</v>
       </c>
     </row>
     <row r="21">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4531076962497637</v>
+        <v>-0.4531076962497638</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.396553498004809</v>
+        <v>-1.39655349800481</v>
       </c>
     </row>
     <row r="23">

--- a/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
+++ b/results/GSE186332/selinexor_predefined_subgroup_validation.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2148486011203609</v>
+        <v>-0.214848601120361</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.53986651829438</v>
+        <v>0.5398665182943801</v>
       </c>
     </row>
     <row r="13">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1922622383257009</v>
+        <v>0.1922622383257012</v>
       </c>
     </row>
   </sheetData>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.800579385935314</v>
+        <v>-0.8005793859353139</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02456567791523645</v>
+        <v>-0.02456567791523639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6078351989334914</v>
+        <v>0.6078351989334916</v>
       </c>
     </row>
     <row r="4">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1058668675511344</v>
+        <v>0.1058668675511345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741701</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.148287671810622</v>
+        <v>-1.148287671810621</v>
       </c>
     </row>
     <row r="7">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.2148486011203609</v>
+        <v>-0.214848601120361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2821614039083842</v>
+        <v>-0.2821614039083846</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06489355131175106</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4192125431629357</v>
+        <v>0.4192125431629362</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04127688761109321</v>
+        <v>0.04127688761109268</v>
       </c>
     </row>
     <row r="10">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2076264540503049</v>
+        <v>-0.2076264540503057</v>
       </c>
     </row>
     <row r="11">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1915672065927819</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3795170631755897</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8718797997519848</v>
+        <v>-0.8718797997519847</v>
       </c>
     </row>
     <row r="14">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1461892299385082</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03897412457640534</v>
+        <v>0.03897412457640585</v>
       </c>
     </row>
     <row r="16">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821825</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6325945707458293</v>
+        <v>-0.6325945707458281</v>
       </c>
     </row>
     <row r="18">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1301722689441585</v>
+        <v>0.1301722689441592</v>
       </c>
     </row>
     <row r="21">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060808</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6256843559636336</v>
+        <v>0.625684355963633</v>
       </c>
     </row>
     <row r="22">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.39655349800481</v>
+        <v>-1.396553498004809</v>
       </c>
     </row>
     <row r="23">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4639826633474022</v>
+        <v>-0.4639826633474023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
